--- a/Companion-Workbooks/Candidate_Register_Workbook.xlsx
+++ b/Companion-Workbooks/Candidate_Register_Workbook.xlsx
@@ -11,11 +11,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WELCOME" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LICENCE" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 1 Investigation" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 2 Candidates" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 3 Containment" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 4 Measurement Study" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 5 Corrective Action" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 12 Investigation" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 13 Candidates" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 14 Containment" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 15 Measurement Study" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 16 Corrective Action" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EXAMPLE A Recurring defect" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EXAMPLE B Intermittent failure" sheetId="12" state="visible" r:id="rId12"/>
@@ -26,9 +26,9 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Cover'!$A$1:$I$31</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'WELCOME'!$A$1:$I$71</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'LICENCE'!$A$1:$I$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Form 1 Investigation'!$A$4:$H$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Form 2 Candidates'!$A$4:$G$304</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Form 5 Corrective Action'!$A$4:$H$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Form 12 Investigation'!$A$4:$H$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Form 13 Candidates'!$A$4:$G$304</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Form 16 Corrective Action'!$A$4:$H$64</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'Dashboard'!$A$1:$J$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="H3" s="43" t="inlineStr">
         <is>
-          <t>NF-CW3  ·  v1.0</t>
+          <t>NF-CW3  ·  v2.0</t>
         </is>
       </c>
     </row>
@@ -2250,14 +2250,14 @@
     <row r="11" ht="46" customHeight="1" s="41">
       <c r="B11" s="46" t="inlineStr">
         <is>
-          <t>The Fourth Time</t>
+          <t>The Norwood Files</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1" s="41">
       <c r="B12" s="47" t="inlineStr">
         <is>
-          <t>A Novel About Root Cause, Corrective Action and Decisions That Were Correct on the Day</t>
+          <t>A Novel About Risk, Audit and Root Cause in a Factory That Stopped Pretending</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
     <row r="15" ht="26" customHeight="1" s="41">
       <c r="B15" s="48" t="inlineStr">
         <is>
-          <t>Companion to Book Three</t>
+          <t>Companion to Part Three — The Investigation</t>
         </is>
       </c>
     </row>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="C21" s="52" t="inlineStr">
         <is>
-          <t>v1.0  ·  NF-CW3</t>
+          <t>v2.0  ·  NF-CW3</t>
         </is>
       </c>
     </row>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="C23" s="52" t="inlineStr">
         <is>
-          <t>Matches the first edition of the book (Editorial Baseline EBL-3.1)</t>
+          <t>Matches the omnibus first edition of The Norwood Files (build RC-Rev9)</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C24" s="52" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>29 August 2026</t>
         </is>
       </c>
     </row>
@@ -2430,23 +2430,23 @@
     </row>
     <row r="5" ht="21.75" customHeight="1" s="41">
       <c r="A5" s="98">
-        <f>COUNTA('Form 1 Investigation'!A5:A64)</f>
+        <f>COUNTA('Form 12 Investigation'!A5:A64)</f>
         <v/>
       </c>
       <c r="C5" s="98">
-        <f>COUNTIF('Form 1 Investigation'!H5:H64,"open")</f>
+        <f>COUNTIF('Form 12 Investigation'!H5:H64,"open")</f>
         <v/>
       </c>
       <c r="E5" s="98">
-        <f>COUNTIF('Form 2 Candidates'!G5:G304,"UNDECIDED")</f>
+        <f>COUNTIF('Form 13 Candidates'!G5:G304,"UNDECIDED")</f>
         <v/>
       </c>
       <c r="G5" s="98">
-        <f>COUNTIF('Form 5 Corrective Action'!H5:H64,"NO EVIDENCE LINE")</f>
+        <f>COUNTIF('Form 16 Corrective Action'!H5:H64,"NO EVIDENCE LINE")</f>
         <v/>
       </c>
       <c r="I5" s="98">
-        <f>COUNTIF('Form 3 Containment'!D5:D64,"EXPIRED*")</f>
+        <f>COUNTIF('Form 14 Containment'!D5:D64,"EXPIRED*")</f>
         <v/>
       </c>
     </row>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="B48" s="103">
-        <f>COUNTIF('Form 5 Corrective Action'!$E$5:$E$64,"5*")</f>
+        <f>COUNTIF('Form 16 Corrective Action'!$E$5:$E$64,"5*")</f>
         <v/>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="B49" s="103">
-        <f>COUNTIF('Form 5 Corrective Action'!$E$5:$E$64,"4*")</f>
+        <f>COUNTIF('Form 16 Corrective Action'!$E$5:$E$64,"4*")</f>
         <v/>
       </c>
     </row>
@@ -2570,7 +2570,7 @@
         </is>
       </c>
       <c r="B50" s="103">
-        <f>COUNTIF('Form 5 Corrective Action'!$E$5:$E$64,"3*")</f>
+        <f>COUNTIF('Form 16 Corrective Action'!$E$5:$E$64,"3*")</f>
         <v/>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
         </is>
       </c>
       <c r="B51" s="103">
-        <f>COUNTIF('Form 5 Corrective Action'!$E$5:$E$64,"2*")</f>
+        <f>COUNTIF('Form 16 Corrective Action'!$E$5:$E$64,"2*")</f>
         <v/>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="B52" s="103">
-        <f>COUNTIF('Form 5 Corrective Action'!$E$5:$E$64,"1*")</f>
+        <f>COUNTIF('Form 16 Corrective Action'!$E$5:$E$64,"1*")</f>
         <v/>
       </c>
     </row>
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="B55" s="103">
-        <f>COUNTIF('Form 2 Candidates'!$D$5:$D$304,"killed")</f>
+        <f>COUNTIF('Form 13 Candidates'!$D$5:$D$304,"killed")</f>
         <v/>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="B56" s="103">
-        <f>COUNTIF('Form 2 Candidates'!$D$5:$D$304,"kept")</f>
+        <f>COUNTIF('Form 13 Candidates'!$D$5:$D$304,"kept")</f>
         <v/>
       </c>
     </row>
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="B60" s="103">
-        <f>COUNTIF('Form 1 Investigation'!$H$5:$H$64,"open")</f>
+        <f>COUNTIF('Form 12 Investigation'!$H$5:$H$64,"open")</f>
         <v/>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="B61" s="103">
-        <f>COUNTIF('Form 1 Investigation'!$H$5:$H$64,"cause identified")</f>
+        <f>COUNTIF('Form 12 Investigation'!$H$5:$H$64,"cause identified")</f>
         <v/>
       </c>
     </row>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="B62" s="103">
-        <f>COUNTIF('Form 1 Investigation'!$H$5:$H$64,"action in place")</f>
+        <f>COUNTIF('Form 12 Investigation'!$H$5:$H$64,"action in place")</f>
         <v/>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="B63" s="103">
-        <f>COUNTIF('Form 1 Investigation'!$H$5:$H$64,"verifying")</f>
+        <f>COUNTIF('Form 12 Investigation'!$H$5:$H$64,"verifying")</f>
         <v/>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="B64" s="103">
-        <f>COUNTIF('Form 1 Investigation'!$H$5:$H$64,"closed")</f>
+        <f>COUNTIF('Form 12 Investigation'!$H$5:$H$64,"closed")</f>
         <v/>
       </c>
     </row>
@@ -2727,7 +2727,7 @@
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW3 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Three&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Three&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2762,7 +2762,7 @@
     <row r="2" ht="15.75" customHeight="1" s="41">
       <c r="A2" s="73" t="inlineStr">
         <is>
-          <t>Worked investigation from Part 2 of the book. Read, do not edit.</t>
+          <t>Worked investigation from Part Three of the book. Read, do not edit.</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW3 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Three&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Three&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2985,7 +2985,7 @@
     <row r="2" ht="15.75" customHeight="1" s="41">
       <c r="A2" s="73" t="inlineStr">
         <is>
-          <t>Worked investigation from Part 2 of the book. Read, do not edit.</t>
+          <t>Worked investigation from Part Three of the book. Read, do not edit.</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW3 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Three&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Three&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3174,7 +3174,7 @@
     <row r="2" ht="15.75" customHeight="1" s="41">
       <c r="A2" s="73" t="inlineStr">
         <is>
-          <t>Worked investigation from Part 2 of the book. Read, do not edit.</t>
+          <t>Worked investigation from Part Three of the book. Read, do not edit.</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW3 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Three&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Three&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3333,7 +3333,7 @@
     <row r="7" ht="15" customHeight="1" s="41">
       <c r="B7" s="108" t="inlineStr">
         <is>
-          <t>Companion to Book Three</t>
+          <t>Companion to Part Three</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
     <row r="9" ht="15" customHeight="1" s="41">
       <c r="B9" s="109" t="inlineStr">
         <is>
-          <t>Document code: NF-CW3 · Identity: NBSM v1.0 · Baseline: EBL-3.1 · Issued 22 August 2026</t>
+          <t>Document code: NF-CW3 · Identity: NBSM v1.0 · Baseline: RC-Rev9 · Issued 29 August 2026</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="H2" s="43" t="inlineStr">
         <is>
-          <t>NF-CW3  ·  v1.0</t>
+          <t>NF-CW3  ·  v2.0</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
     <row r="8" ht="14" customHeight="1" s="41">
       <c r="B8" s="56" t="inlineStr">
         <is>
-          <t>This workbook is the working half of Book Three of The Norwood Files. It carries the forms from the book with the rules already written into the formulas, so that the method can be run on a real process instead of read about. Its subject is investigating a defect that has come back: classifying previous investigations, containment with an expiry, separating a cause from a companion, and verifying against exposure rather than the calendar.</t>
+          <t>This workbook is the working half of Part Three of The Norwood Files. It carries the forms from the book with the rules already written into the formulas, so that the method can be run on a real process instead of read about. Its subject is investigating a defect that has come back: classifying previous investigations, containment with an expiry, separating a cause from a companion, and verifying against exposure rather than the calendar.</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
     <row r="22" ht="14" customHeight="1" s="41">
       <c r="B22" s="56" t="inlineStr">
         <is>
-          <t>The numbered sheets carry the same Form numbers as the book. Form 3 in the book is Form 3 in this file. The sheets prefixed EXAMPLE are the worked cases from the book, complete and populated, so that you can see how a row behaves before you clear it and start on your own process.</t>
+          <t>The numbered sheets carry the same Form numbers as the book. Form 13 in the book is Form 13 in this file. The sheets prefixed EXAMPLE are the worked cases from the book, complete and populated, so that you can see how a row behaves before you clear it and start on your own process.</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
     <row r="43" ht="28" customHeight="1" s="41">
       <c r="B43" s="60" t="inlineStr">
         <is>
-          <t>Form 1 Investigation</t>
+          <t>Form 12 Investigation</t>
         </is>
       </c>
       <c r="C43" s="61" t="inlineStr">
@@ -3628,7 +3628,7 @@
     <row r="44" ht="28" customHeight="1" s="41">
       <c r="B44" s="60" t="inlineStr">
         <is>
-          <t>Form 2 Candidates</t>
+          <t>Form 13 Candidates</t>
         </is>
       </c>
       <c r="C44" s="61" t="inlineStr">
@@ -3645,7 +3645,7 @@
     <row r="45" ht="28" customHeight="1" s="41">
       <c r="B45" s="60" t="inlineStr">
         <is>
-          <t>Form 3 Containment</t>
+          <t>Form 14 Containment</t>
         </is>
       </c>
       <c r="C45" s="61" t="inlineStr">
@@ -3662,7 +3662,7 @@
     <row r="46" ht="39.5" customHeight="1" s="41">
       <c r="B46" s="60" t="inlineStr">
         <is>
-          <t>Form 4 Measurement Study</t>
+          <t>Form 15 Measurement Study</t>
         </is>
       </c>
       <c r="C46" s="61" t="inlineStr">
@@ -3679,7 +3679,7 @@
     <row r="47" ht="39.5" customHeight="1" s="41">
       <c r="B47" s="60" t="inlineStr">
         <is>
-          <t>Form 5 Corrective Action</t>
+          <t>Form 16 Corrective Action</t>
         </is>
       </c>
       <c r="C47" s="61" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="H2" s="43" t="inlineStr">
         <is>
-          <t>NF-CW3  ·  v1.0</t>
+          <t>NF-CW3  ·  v2.0</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       <c r="C9" s="50" t="n"/>
       <c r="D9" s="68" t="inlineStr">
         <is>
-          <t>The Norwood Files — Companion to Book Three</t>
+          <t>The Norwood Files — Companion to Part Three</t>
         </is>
       </c>
       <c r="E9" s="50" t="n"/>
@@ -3982,7 +3982,7 @@
       <c r="C10" s="50" t="n"/>
       <c r="D10" s="68" t="inlineStr">
         <is>
-          <t>The Fourth Time</t>
+          <t>The Norwood Files</t>
         </is>
       </c>
       <c r="E10" s="50" t="n"/>
@@ -4016,7 +4016,7 @@
       <c r="C12" s="50" t="n"/>
       <c r="D12" s="68" t="inlineStr">
         <is>
-          <t>v1.0</t>
+          <t>v2.0</t>
         </is>
       </c>
       <c r="E12" s="50" t="n"/>
@@ -4033,7 +4033,7 @@
       <c r="C13" s="50" t="n"/>
       <c r="D13" s="68" t="inlineStr">
         <is>
-          <t>v1.0  ·  issued 22 August 2026</t>
+          <t>v2.0  ·  issued 29 August 2026</t>
         </is>
       </c>
       <c r="E13" s="50" t="n"/>
@@ -4067,7 +4067,7 @@
       <c r="C15" s="50" t="n"/>
       <c r="D15" s="68" t="inlineStr">
         <is>
-          <t>EBL-3.1</t>
+          <t>RC-Rev9</t>
         </is>
       </c>
       <c r="E15" s="50" t="n"/>
@@ -4141,7 +4141,7 @@
     <row r="27" ht="13" customHeight="1" s="41">
       <c r="B27" s="69" t="inlineStr">
         <is>
-          <t>This workbook accompanies The Fourth Time and is supplied free of charge with the book. You may use it, adapt it and reproduce it inside your own organization for your own quality management system.</t>
+          <t>This workbook accompanies The Norwood Files and is supplied free of charge with the book. You may use it, adapt it and reproduce it inside your own organization for your own quality management system.</t>
         </is>
       </c>
     </row>
@@ -4242,14 +4242,14 @@
     <row r="1" ht="25.5" customHeight="1" s="41">
       <c r="A1" s="72" t="inlineStr">
         <is>
-          <t>THE FOURTH TIME—COMPANION WORKBOOK</t>
+          <t>THE NORWOOD FILES — PART THREE COMPANION</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" s="41">
       <c r="A2" s="73" t="inlineStr">
         <is>
-          <t>The forms from Part 3. Free, no sign-up. Everything here is also printed in the book.</t>
+          <t>The forms from Part Five. Free, no sign-up. Everything here is also printed in the book.</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4264,7 @@
     <row r="5" ht="25.5" customHeight="1" s="41">
       <c r="B5" s="75" t="inlineStr">
         <is>
-          <t>The investigation record, candidate register, containment record, attribute measurement study and corrective action record from Part 3, plus the three worked investigations from Part 2.</t>
+          <t>The investigation record, candidate register, containment record, attribute measurement study and corrective action record from Part Five, plus the three worked investigations from Part Three.</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
     <row r="8" ht="25.5" customHeight="1" s="41">
       <c r="B8" s="75" t="inlineStr">
         <is>
-          <t>1.  Open 'Form 1 Investigation'. Fill the previous-occurrence rows first. The sequence of hierarchy levels across them is the finding before you examine any evidence.</t>
+          <t>1.  Open 'Form 12 Investigation'. Fill the previous-occurrence rows first. The sequence of hierarchy levels across them is the finding before you examine any evidence.</t>
         </is>
       </c>
     </row>
@@ -4299,28 +4299,28 @@
     <row r="10" ht="25.5" customHeight="1" s="41">
       <c r="B10" s="75" t="inlineStr">
         <is>
-          <t>3.  Every candidate goes on 'Form 2 Candidates' and ends killed or kept. The sheet turns red on any row left undecided.</t>
+          <t>3.  Every candidate goes on 'Form 13 Candidates' and ends killed or kept. The sheet turns red on any row left undecided.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="41">
       <c r="B11" s="75" t="inlineStr">
         <is>
-          <t>4.  'Form 3 Containment' has an expiry date, not a review date. It turns red on the day.</t>
+          <t>4.  'Form 14 Containment' has an expiry date, not a review date. It turns red on the day.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="41">
       <c r="B12" s="75" t="inlineStr">
         <is>
-          <t>5.  Run 'Form 4 Measurement Study' before trusting any pass/fail data at all.</t>
+          <t>5.  Run 'Form 15 Measurement Study' before trusting any pass/fail data at all.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="25.5" customHeight="1" s="41">
       <c r="B13" s="75" t="inlineStr">
         <is>
-          <t>6.  'Form 5 Corrective Action' calculates the minimum verification period from the defect’s own recurrence history.</t>
+          <t>6.  'Form 16 Corrective Action' calculates the minimum verification period from the defect’s own recurrence history.</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
     <row r="19" ht="39" customHeight="1" s="41">
       <c r="B19" s="75" t="inlineStr">
         <is>
-          <t>The three sheets prefixed EXAMPLE are the worked investigations from Part 2, with every candidate and the evidence that killed or kept it. Read the candidate register rather than the conclusion. The conclusions belong to a plant that is not yours.</t>
+          <t>The three sheets prefixed EXAMPLE are the worked investigations from Part Three, with every candidate and the evidence that killed or kept it. Read the candidate register rather than the conclusion. The conclusions belong to a plant that is not yours.</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4384,7 @@
     <row r="23" ht="15" customHeight="1" s="41">
       <c r="A23" s="76" t="inlineStr">
         <is>
-          <t>The Norwood Files · Companion to Book Three · v1.0 · issued 22 August 2026 · matches the first edition (Editorial Baseline EBL-3.1)</t>
+          <t>The Norwood Files · Companion to Part Three · v2.0 · issued 29 August 2026 · matches the omnibus first edition (build RC-Rev9)</t>
         </is>
       </c>
     </row>
@@ -4399,7 +4399,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW3 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Three&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Three&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5130,7 +5130,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW3 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Three&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Three&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -8845,7 +8845,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW3 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Three&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Three&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -9486,7 +9486,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW3 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Three&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Three&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -9501,12 +9501,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="71" min="1" max="1"/>
     <col width="17" customWidth="1" style="71" min="2" max="5"/>
-    <col width="15" customWidth="1" style="71" min="6" max="7"/>
+    <col width="15" customWidth="1" style="71" min="6" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="41">
@@ -9557,7 +9557,12 @@
       </c>
       <c r="G4" s="77" t="inlineStr">
         <is>
-          <t>A and B agree</t>
+          <t>B self-agrees</t>
+        </is>
+      </c>
+      <c r="H4" s="77" t="inlineStr">
+        <is>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9581,11 @@
         <v/>
       </c>
       <c r="G5" s="89">
-        <f>IF(OR(B5="",D5=""),"",IF(EXACT(B5,D5),"yes","NO"))</f>
+        <f>IF(OR(D5="",E5=""),"",IF(EXACT(D5,E5),"yes","NO"))</f>
+        <v/>
+      </c>
+      <c r="H5" s="89">
+        <f>IF(OR(F5="",G5=""),"",IF(OR(F5="NO",G5="NO"),"grader disagrees with herself",IF(EXACT(B5,D5),"all agree","graders disagree")))</f>
         <v/>
       </c>
     </row>
@@ -9595,7 +9604,11 @@
         <v/>
       </c>
       <c r="G6" s="89">
-        <f>IF(OR(B6="",D6=""),"",IF(EXACT(B6,D6),"yes","NO"))</f>
+        <f>IF(OR(D6="",E6=""),"",IF(EXACT(D6,E6),"yes","NO"))</f>
+        <v/>
+      </c>
+      <c r="H6" s="89">
+        <f>IF(OR(F6="",G6=""),"",IF(OR(F6="NO",G6="NO"),"grader disagrees with herself",IF(EXACT(B6,D6),"all agree","graders disagree")))</f>
         <v/>
       </c>
     </row>
@@ -9614,7 +9627,11 @@
         <v/>
       </c>
       <c r="G7" s="89">
-        <f>IF(OR(B7="",D7=""),"",IF(EXACT(B7,D7),"yes","NO"))</f>
+        <f>IF(OR(D7="",E7=""),"",IF(EXACT(D7,E7),"yes","NO"))</f>
+        <v/>
+      </c>
+      <c r="H7" s="89">
+        <f>IF(OR(F7="",G7=""),"",IF(OR(F7="NO",G7="NO"),"grader disagrees with herself",IF(EXACT(B7,D7),"all agree","graders disagree")))</f>
         <v/>
       </c>
     </row>
@@ -9633,7 +9650,11 @@
         <v/>
       </c>
       <c r="G8" s="89">
-        <f>IF(OR(B8="",D8=""),"",IF(EXACT(B8,D8),"yes","NO"))</f>
+        <f>IF(OR(D8="",E8=""),"",IF(EXACT(D8,E8),"yes","NO"))</f>
+        <v/>
+      </c>
+      <c r="H8" s="89">
+        <f>IF(OR(F8="",G8=""),"",IF(OR(F8="NO",G8="NO"),"grader disagrees with herself",IF(EXACT(B8,D8),"all agree","graders disagree")))</f>
         <v/>
       </c>
     </row>
@@ -9652,7 +9673,11 @@
         <v/>
       </c>
       <c r="G9" s="89">
-        <f>IF(OR(B9="",D9=""),"",IF(EXACT(B9,D9),"yes","NO"))</f>
+        <f>IF(OR(D9="",E9=""),"",IF(EXACT(D9,E9),"yes","NO"))</f>
+        <v/>
+      </c>
+      <c r="H9" s="89">
+        <f>IF(OR(F9="",G9=""),"",IF(OR(F9="NO",G9="NO"),"grader disagrees with herself",IF(EXACT(B9,D9),"all agree","graders disagree")))</f>
         <v/>
       </c>
     </row>
@@ -9671,7 +9696,11 @@
         <v/>
       </c>
       <c r="G10" s="89">
-        <f>IF(OR(B10="",D10=""),"",IF(EXACT(B10,D10),"yes","NO"))</f>
+        <f>IF(OR(D10="",E10=""),"",IF(EXACT(D10,E10),"yes","NO"))</f>
+        <v/>
+      </c>
+      <c r="H10" s="89">
+        <f>IF(OR(F10="",G10=""),"",IF(OR(F10="NO",G10="NO"),"grader disagrees with herself",IF(EXACT(B10,D10),"all agree","graders disagree")))</f>
         <v/>
       </c>
     </row>
@@ -9690,7 +9719,11 @@
         <v/>
       </c>
       <c r="G11" s="89">
-        <f>IF(OR(B11="",D11=""),"",IF(EXACT(B11,D11),"yes","NO"))</f>
+        <f>IF(OR(D11="",E11=""),"",IF(EXACT(D11,E11),"yes","NO"))</f>
+        <v/>
+      </c>
+      <c r="H11" s="89">
+        <f>IF(OR(F11="",G11=""),"",IF(OR(F11="NO",G11="NO"),"grader disagrees with herself",IF(EXACT(B11,D11),"all agree","graders disagree")))</f>
         <v/>
       </c>
     </row>
@@ -9709,7 +9742,11 @@
         <v/>
       </c>
       <c r="G12" s="89">
-        <f>IF(OR(B12="",D12=""),"",IF(EXACT(B12,D12),"yes","NO"))</f>
+        <f>IF(OR(D12="",E12=""),"",IF(EXACT(D12,E12),"yes","NO"))</f>
+        <v/>
+      </c>
+      <c r="H12" s="89">
+        <f>IF(OR(F12="",G12=""),"",IF(OR(F12="NO",G12="NO"),"grader disagrees with herself",IF(EXACT(B12,D12),"all agree","graders disagree")))</f>
         <v/>
       </c>
     </row>
@@ -9728,7 +9765,11 @@
         <v/>
       </c>
       <c r="G13" s="89">
-        <f>IF(OR(B13="",D13=""),"",IF(EXACT(B13,D13),"yes","NO"))</f>
+        <f>IF(OR(D13="",E13=""),"",IF(EXACT(D13,E13),"yes","NO"))</f>
+        <v/>
+      </c>
+      <c r="H13" s="89">
+        <f>IF(OR(F13="",G13=""),"",IF(OR(F13="NO",G13="NO"),"grader disagrees with herself",IF(EXACT(B13,D13),"all agree","graders disagree")))</f>
         <v/>
       </c>
     </row>
@@ -9747,7 +9788,11 @@
         <v/>
       </c>
       <c r="G14" s="89">
-        <f>IF(OR(B14="",D14=""),"",IF(EXACT(B14,D14),"yes","NO"))</f>
+        <f>IF(OR(D14="",E14=""),"",IF(EXACT(D14,E14),"yes","NO"))</f>
+        <v/>
+      </c>
+      <c r="H14" s="89">
+        <f>IF(OR(F14="",G14=""),"",IF(OR(F14="NO",G14="NO"),"grader disagrees with herself",IF(EXACT(B14,D14),"all agree","graders disagree")))</f>
         <v/>
       </c>
     </row>
@@ -9767,7 +9812,7 @@
       </c>
       <c r="B17" s="92" t="n"/>
       <c r="C17" s="93">
-        <f>COUNTIF(F5:F14,"yes")&amp;" of "&amp;COUNTA(F5:F14)</f>
+        <f>IF(COUNTA(B5:E14)=0,"",COUNTIF(F5:F14,"yes")&amp;" of "&amp;SUMPRODUCT(--(F5:F14&lt;&gt;"")))</f>
         <v/>
       </c>
       <c r="D17" s="94" t="inlineStr">
@@ -9779,29 +9824,46 @@
     <row r="18" ht="33.75" customHeight="1" s="41">
       <c r="A18" s="91" t="inlineStr">
         <is>
-          <t>Graders agree with each other</t>
+          <t>Grader B agrees with herself</t>
         </is>
       </c>
       <c r="B18" s="92" t="n"/>
       <c r="C18" s="93">
-        <f>COUNTIF(G5:G14,"yes")&amp;" of "&amp;COUNTA(G5:G14)</f>
+        <f>IF(COUNTA(B5:E14)=0,"",COUNTIF(G5:G14,"yes")&amp;" of "&amp;SUMPRODUCT(--(G5:G14&lt;&gt;"")))</f>
         <v/>
       </c>
       <c r="D18" s="94" t="inlineStr">
         <is>
-          <t>Reproducibility. Materially worse than self-agreement means the difference is a person.</t>
+          <t>Repeatability of the second grader. Both are rated, not one.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="33.75" customHeight="1" s="41">
       <c r="A19" s="91" t="inlineStr">
         <is>
+          <t>Graders agree with each other</t>
+        </is>
+      </c>
+      <c r="B19" s="92" t="n"/>
+      <c r="C19" s="93">
+        <f>IF(COUNTA(B5:E14)=0,"",(SUMPRODUCT(--(H5:H14&lt;&gt;""))-COUNTIF(H5:H14,"graders disagree"))&amp;" of "&amp;SUMPRODUCT(--(H5:H14&lt;&gt;"")))</f>
+        <v/>
+      </c>
+      <c r="D19" s="94" t="inlineStr">
+        <is>
+          <t>Reproducibility. Materially worse than self-agreement means the difference is a person.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="33.75" customHeight="1" s="41">
+      <c r="A20" s="91" t="inlineStr">
+        <is>
           <t>Agreement with a reference</t>
         </is>
       </c>
-      <c r="B19" s="92" t="n"/>
-      <c r="C19" s="93" t="n"/>
-      <c r="D19" s="94" t="inlineStr">
+      <c r="B20" s="92" t="n"/>
+      <c r="C20" s="93" t="n"/>
+      <c r="D20" s="94" t="inlineStr">
         <is>
           <t>If no reference standard exists, that is itself the finding.</t>
         </is>
@@ -9809,13 +9871,15 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="D17:G17"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="D19:G19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="D20:G20"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A18:B18"/>
   </mergeCells>
@@ -9846,7 +9910,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW3 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Three&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Three&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -10925,7 +10989,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW3 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Three&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Three&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
